--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B3" t="n">
-        <v>98012</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R3" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R2" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R3" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467975</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467975</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R3" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R2" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R3" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R2" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>98030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R3" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 9661-2023 artfynd.xlsx
+++ b/artfynd/A 9661-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467975</v>
+        <v>121467937</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530600</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6514306</v>
+        <v>6514570</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467937</v>
+        <v>121467975</v>
       </c>
       <c r="B3" t="n">
-        <v>98030</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530586</v>
+        <v>530600</v>
       </c>
       <c r="R3" t="n">
-        <v>6514570</v>
+        <v>6514306</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
